--- a/data/template_siswa.xlsx
+++ b/data/template_siswa.xlsx
@@ -7,7 +7,7 @@
     <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
-    <sheet name="Worksheet" sheetId="1" r:id="rId4"/>
+    <sheet name="Template Siswa" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="7">
   <si>
     <t>NISN</t>
   </si>
@@ -23,10 +23,19 @@
     <t>Nama Siswa</t>
   </si>
   <si>
+    <t>Jenis Kelamin (L/P)</t>
+  </si>
+  <si>
     <t>Nama Kelas</t>
   </si>
   <si>
-    <t>Alamat</t>
+    <t>Tempat Lahir</t>
+  </si>
+  <si>
+    <t>Tanggal Lahir</t>
+  </si>
+  <si>
+    <t>Nama Wali</t>
   </si>
 </sst>
 </file>
@@ -63,17 +72,32 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF4B49AC"/>
+        <fgColor rgb="FF4F81BD"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -82,9 +106,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -384,16 +406,19 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="8.141" bestFit="true" customWidth="true" style="0"/>
-    <col min="2" max="2" width="15.139" bestFit="true" customWidth="true" style="0"/>
-    <col min="3" max="3" width="15.139" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="10.426" bestFit="true" customWidth="true" style="0"/>
+    <col min="1" max="1" width="5.856" bestFit="true" customWidth="true" style="0"/>
+    <col min="2" max="2" width="12.854" bestFit="true" customWidth="true" style="0"/>
+    <col min="3" max="3" width="23.423" bestFit="true" customWidth="true" style="0"/>
+    <col min="4" max="4" width="12.854" bestFit="true" customWidth="true" style="0"/>
+    <col min="5" max="5" width="15.282" bestFit="true" customWidth="true" style="0"/>
+    <col min="6" max="6" width="16.425" bestFit="true" customWidth="true" style="0"/>
+    <col min="7" max="7" width="11.711" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -405,6 +430,15 @@
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
